--- a/plantillas/Informe_Tasacion_Agrosalta.xlsx
+++ b/plantillas/Informe_Tasacion_Agrosalta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diego\Documents\ESTUDIO DAG\PENDIENTES\1 - pendientes\INFORMES TIPOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6745C473-9789-4782-94C6-FE1007E47BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63A5FD9-20D5-4278-BEA4-77E1FDAF70C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="384" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -805,116 +805,116 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -940,13 +940,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -961,8 +961,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="11551920"/>
-          <a:ext cx="9243060" cy="807720"/>
+          <a:off x="0" y="12062460"/>
+          <a:ext cx="9227820" cy="830580"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1291,15 +1291,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>53339</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>769620</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1316,8 +1316,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="251460" y="10424159"/>
-          <a:ext cx="1676400" cy="266701"/>
+          <a:off x="167640" y="12527279"/>
+          <a:ext cx="1676400" cy="388621"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1375,15 +1375,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>53341</xdr:rowOff>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1400,8 +1400,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3794760" y="10995661"/>
-          <a:ext cx="1661160" cy="152400"/>
+          <a:off x="3733800" y="12550141"/>
+          <a:ext cx="1889760" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1459,15 +1459,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>473175</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>70176</xdr:rowOff>
+      <xdr:colOff>396975</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>24456</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1484,8 +1484,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8686800" y="10988040"/>
-          <a:ext cx="1098015" cy="207336"/>
+          <a:off x="8526780" y="12473940"/>
+          <a:ext cx="1098015" cy="230196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1792,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -1817,42 +1817,42 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="80"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="44"/>
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="80"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="4.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1866,16 +1866,16 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="56"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="14"/>
       <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
       <c r="G7" s="11" t="s">
         <v>21</v>
       </c>
@@ -1895,27 +1895,27 @@
       <c r="A9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
       <c r="D9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
       <c r="G9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="70"/>
     </row>
     <row r="11" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
@@ -1949,416 +1949,416 @@
       <c r="A13" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
       <c r="D13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="62"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="72"/>
     </row>
     <row r="14" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="60"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="70"/>
     </row>
     <row r="15" spans="1:8" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
       <c r="D15" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="75"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="48"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66" t="s">
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="67"/>
+      <c r="H17" s="79"/>
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="23"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="77"/>
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="23"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="77"/>
     </row>
     <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="23"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="23"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="48"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="77"/>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="23"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="77"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="23"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="77"/>
     </row>
     <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="23"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="23"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="23"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="48"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="48"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="48"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="23"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="77"/>
     </row>
     <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="23"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="48"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="23"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="48"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="23"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="48"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="23"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="48"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="77"/>
     </row>
     <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="23"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="48"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="77"/>
     </row>
     <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="23"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="23"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="48"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="23"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="23"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="48"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="23"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="23"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="48"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="77"/>
     </row>
     <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="23"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="48"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="77"/>
     </row>
     <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="23"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="48"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="77"/>
     </row>
     <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="23"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="48"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="77"/>
     </row>
     <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="23"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="48"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="77"/>
     </row>
     <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="23"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="48"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="77"/>
     </row>
     <row r="51" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="75" t="s">
+      <c r="B51" s="63"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
-      <c r="H51" s="77"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="58"/>
     </row>
     <row r="52" spans="1:8" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
+      <c r="A52" s="51"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="35" t="s">
         <v>5</v>
       </c>
@@ -2368,15 +2368,15 @@
       <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="78" t="s">
+      <c r="G52" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="79"/>
+      <c r="H52" s="61"/>
     </row>
     <row r="53" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="36" t="s">
         <v>10</v>
       </c>
@@ -2384,16 +2384,16 @@
       <c r="F53" s="38">
         <v>120000</v>
       </c>
-      <c r="G53" s="49">
+      <c r="G53" s="55">
         <f t="shared" ref="G53" si="0">+E53*F53</f>
         <v>0</v>
       </c>
-      <c r="H53" s="49"/>
+      <c r="H53" s="55"/>
     </row>
     <row r="54" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
+      <c r="A54" s="51"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="36" t="s">
         <v>11</v>
       </c>
@@ -2401,16 +2401,16 @@
       <c r="F54" s="38">
         <v>120000</v>
       </c>
-      <c r="G54" s="49">
+      <c r="G54" s="55">
         <f t="shared" ref="G54:G56" si="1">+E54*F54</f>
         <v>0</v>
       </c>
-      <c r="H54" s="49"/>
+      <c r="H54" s="55"/>
     </row>
     <row r="55" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
+      <c r="A55" s="51"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="36" t="s">
         <v>12</v>
       </c>
@@ -2418,16 +2418,16 @@
       <c r="F55" s="38">
         <v>50000</v>
       </c>
-      <c r="G55" s="49">
+      <c r="G55" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H55" s="49"/>
+      <c r="H55" s="55"/>
     </row>
     <row r="56" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
+      <c r="A56" s="51"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="36" t="s">
         <v>13</v>
       </c>
@@ -2435,98 +2435,98 @@
       <c r="F56" s="38">
         <v>50000</v>
       </c>
-      <c r="G56" s="49">
+      <c r="G56" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H56" s="49"/>
-    </row>
-    <row r="57" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
+      <c r="H56" s="55"/>
+    </row>
+    <row r="57" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="51"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="44"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-    </row>
-    <row r="58" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+    </row>
+    <row r="58" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="51"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="24"/>
       <c r="E58" s="25"/>
       <c r="F58" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="73">
+      <c r="G58" s="53">
         <f>SUM(G53:H57)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="74"/>
-    </row>
-    <row r="59" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A59" s="53"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
+      <c r="H58" s="54"/>
+    </row>
+    <row r="59" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="51"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="24"/>
       <c r="E59" s="25"/>
       <c r="F59" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="73">
+      <c r="G59" s="53">
         <f>SUM(G18:H50)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="74"/>
-    </row>
-    <row r="60" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A60" s="53"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
+      <c r="H59" s="54"/>
+    </row>
+    <row r="60" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="51"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="24"/>
       <c r="E60" s="25"/>
       <c r="F60" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="73">
+      <c r="G60" s="53">
         <f>+H11</f>
         <v>0</v>
       </c>
-      <c r="H60" s="74"/>
-    </row>
-    <row r="61" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A61" s="53"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
+      <c r="H60" s="54"/>
+    </row>
+    <row r="61" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="51"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="24"/>
       <c r="E61" s="25"/>
       <c r="F61" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G61" s="71">
+      <c r="G61" s="49">
         <f>+G58+G59-G60</f>
         <v>0</v>
       </c>
-      <c r="H61" s="72"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H61" s="50"/>
+    </row>
+    <row r="62" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="F62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="27"/>
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
@@ -2536,9 +2536,90 @@
       <c r="G65" s="28"/>
       <c r="H65" s="29"/>
     </row>
-    <row r="66" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="A59:C59"/>
@@ -2563,84 +2644,6 @@
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
